--- a/output/第10期計画_将来推計_第3段階_給付費と保険料.xlsx
+++ b/output/第10期計画_将来推計_第3段階_給付費と保険料.xlsx
@@ -139,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -181,6 +181,12 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -650,7 +656,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計による給付費（3年計 9,267.4百万円）に、令和6年度決算による割増率1.0591を乗じる</t>
+          <t>見える化システムの自然体推計による給付費（3年計 9267.4百万円）を人口の基礎の変更により1.0233倍に置き直し、令和6年度決算による割増率1.0591を乗じる</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -866,7 +872,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>推計上の第1号被保険者数3年計27,230人に、令和6年度の実績による係数0.9914を乗じる</t>
+          <t>推計上の第1号被保険者数3年計27,539人に、令和6年度の実績による係数0.9914を乗じる</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -1186,7 +1192,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>見える化システムは第10期3年平均の保険料基準額を6,238円と出力しています。本表の基本ケース6684円との差+446円について、受託者が確認できた範囲を示します。</t>
+          <t>見える化システムは第10期3年平均の保険料基準額を6,238円と出力しています。本表の基本ケース6755円との差+517円について、受託者が確認できた範囲を示します。</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1251,12 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>6684円</t>
+          <t>6755円</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>+446円</t>
+          <t>+517円</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1275,12 +1281,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>6229円</t>
+          <t>6159円</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>-9円</t>
+          <t>-79円</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1389,7 +1395,7 @@
     <row r="13" ht="140" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計6,238円は、内訳が出力されないため、項目ごとに突き合わせることができません。ただし、給付費を第9期の実績年率で置いた場合の本表の値は6229円で、6,238円との差は9円（0.1％）にとどまります。他の前提（収納率・基金取崩額・第1号負担割合）は同じであるため、見える化の保険料の推計は給付費を第9期の実績の水準で置いており、同じ見える化システムが出力する自然体給付費推計の伸びを織り込んでいない可能性があります。これは受託者の推定であり、確認したものではありません。
+          <t>見える化システムの自然体推計6,238円は、内訳が出力されないため、項目ごとに突き合わせることができません。ただし、給付費を第9期の実績年率で置いた場合の本表の値は6159円で、6,238円との差は9円（0.1％）にとどまります。他の前提（収納率・基金取崩額・第1号負担割合）は同じであるため、見える化の保険料の推計は給付費を第9期の実績の水準で置いており、同じ見える化システムが出力する自然体給付費推計の伸びを織り込んでいない可能性があります。これは受託者の推定であり、確認したものではありません。
 第10期の計画に用いる値は、見える化の出力をそのまま採るのではなく、本表のように内訳を組み立てたうえで決めることが必要です。内訳を示せなければ、住民及び委員に対して保険料の水準を説明することができないためです。
 計画素案 第6章第6節2に掲載している「見える化自然体推計（基準ケース）6,238円」は、本表の完成後に、本表の基本ケースへ置き換えることを提案します。</t>
         </is>
@@ -1491,7 +1497,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>±455円程度</t>
+          <t>±596円程度</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -1521,7 +1527,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>1ポイントで約323円</t>
+          <t>1ポイントで約327円</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1551,7 +1557,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>取崩額により▲722円まで</t>
+          <t>取崩額により▲714円まで</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1611,7 +1617,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>-59円</t>
+          <t>-60円</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -1641,7 +1647,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>1％で約40円</t>
+          <t>1％で約41円</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1731,7 +1737,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>+279円（第8期の実績水準とした場合）</t>
+          <t>+282円（第8期の実績水準とした場合）</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1743,8 +1749,8 @@
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>注1）本表の基本ケース6684円は暫定の値です。上記9件が確定するまでは、条例で採用する基準額の算定には用いられません。
-注2）第9期の条例基準額は6,400円でした。本表の基本ケースはこれを+284円上回ります。
+          <t>注1）本表の基本ケース6755円は暫定の値です。上記9件が確定するまでは、条例で採用する基準額の算定には用いられません。
+注2）第9期の条例基準額は6,400円でした。本表の基本ケースはこれを+355円上回ります。
 注3）第10期の保険料は、水準そのものよりも「どの前提でその水準になるか」を示すことが重要です。本表は、前提を1つずつ確認できる形にすることを目的としています。</t>
         </is>
       </c>
@@ -1765,7 +1771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1963,199 +1969,351 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>【2　総給付費から標準給付費見込額への割増率】</t>
+          <t>【1の2　人口の基礎を総合戦略ベースに改めたことによる置換え】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>第10期計</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>認定者数　案A（社人研）</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>1995</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>5999</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの自然体推計の基礎</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>認定者数　案C（総合戦略ベース）</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>2046</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>2067</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>6139</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>将来推計 第1段階 03シート・シナリオ②</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>置換率（案C÷案A）</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1.0152</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>1.0231</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>1.0314</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>1.0233</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>給付費に乗じる</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>置換え後の給付費</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>3103.2</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>3161.7</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>3218.6</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>9483.5</v>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>本表で用いる値</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>単位：人・百万円。見える化システムの自然体推計は社人研の推計人口を基礎としています。令和8年8月31日のご指示により人口の基礎を総合戦略ベース（案C）に改めたため、給付費を認定者数の比で置き直しました。サービス構成比は変えていません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>【2　総給付費から標準給付費見込額への割増率】</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>算定の経路</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>総給付費（円）</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>標準給付費見込額（円）</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>割増率</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>採否</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>令和6年度決算</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B22" s="15" t="n">
         <v>2817194455</v>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C22" s="15" t="n">
         <v>2983668988</v>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D22" s="15" t="n">
         <v>1.05909</v>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>採用</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>保険給付費（款2）＝介護サービス等諸費＋その他諸費＋高額介護等サービス費＋高額医療合算介護等サービス費＋特定入所者介護等サービス費</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>第9期計画</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B23" s="15" t="n">
         <v>8905234000</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C23" s="15" t="n">
         <v>9519211524</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D23" s="15" t="n">
         <v>1.06895</v>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>感度</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>見える化システムの第9期計画給付費8,905,234千円と、第9期計画の標準給付費見込額との比。06シートで感度を示す</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>【3　標準給付費見込額（A）】</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>第10期計</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>第9期計画との比</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>標準給付費見込額</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>3237327469</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>3272807062</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>3304897559</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>9815032090</v>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>103.1％</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="B27" s="18" t="n">
+        <v>3286614092</v>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>3348497337</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>3408750262</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>10043861690</v>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>105.5％</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>（参考）第9期計画</t>
         </is>
       </c>
-      <c r="B21" s="15" t="n">
+      <c r="B28" s="15" t="n">
         <v>3127780210</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C28" s="15" t="n">
         <v>3184593217</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D28" s="15" t="n">
         <v>3206838097</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E28" s="15" t="n">
         <v>9519211524</v>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>100.0％</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="68" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>注1）単位は円。第10期の標準給付費見込額は第9期計画の103.1％です。
+    <row r="30" ht="68" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>注1）単位は円。第10期の標準給付費見込額は第9期計画の105.5％です。
 注2）割増率は、高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるためのものです。令和6年度の決算では、給付費2,817,194,455円に対し保険給付費（款2）が2,983,668,988円で、差は166,474,533円です。
 注3）令和7年度の決算が確定した時点で割増率を検証します。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2341,13 +2499,13 @@
           <t>計</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="18" t="n">
         <v>186011000</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="18" t="n">
         <v>183384259</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="18" t="n">
         <v>2626741</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -2406,16 +2564,16 @@
           <t>地域支援事業費</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="18" t="n">
         <v>183384259</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="18" t="n">
         <v>183384259</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="18" t="n">
         <v>183384259</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="18" t="n">
         <v>550152777</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -2551,14 +2709,14 @@
         </is>
       </c>
       <c r="C6" s="15" t="n">
-        <v>9815032090</v>
+        <v>10043861690</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>9519211524</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>103.1％</t>
+          <t>105.5％</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -2596,7 +2754,7 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>①</t>
         </is>
@@ -2606,15 +2764,15 @@
           <t>合計（A＋B）</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n">
-        <v>10365184867</v>
-      </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="18" t="n">
+        <v>10594014467</v>
+      </c>
+      <c r="D8" s="18" t="n">
         <v>10112869524</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>102.5％</t>
+          <t>104.8％</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -2624,7 +2782,7 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>②</t>
         </is>
@@ -2634,15 +2792,15 @@
           <t>調整交付金の算定基礎（A＋総合事業費）</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
-        <v>10118855953</v>
-      </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="18" t="n">
+        <v>10347685553</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <v>9850309520</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>102.7％</t>
+          <t>105.0％</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -2663,14 +2821,14 @@
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>2383992519</v>
+        <v>2436623327</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>2325959991</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>102.5％</t>
+          <t>104.8％</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -2691,14 +2849,14 @@
         </is>
       </c>
       <c r="C11" s="15" t="n">
-        <v>505942798</v>
+        <v>517384278</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>492515476</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>102.7％</t>
+          <t>105.0％</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -2719,14 +2877,14 @@
         </is>
       </c>
       <c r="C12" s="15" t="n">
-        <v>746313572</v>
+        <v>763190839</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>726507000</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>102.7％</t>
+          <t>105.0％</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2764,7 +2922,7 @@
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
@@ -2774,15 +2932,15 @@
           <t>保険料収納必要額（C＋D－E－I）</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n">
-        <v>2143621745</v>
-      </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="18" t="n">
+        <v>2190816766</v>
+      </c>
+      <c r="D14" s="18" t="n">
         <v>2051968467</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>104.5％</t>
+          <t>106.8％</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -2837,12 +2995,12 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>2,383,992,519＋505,942,798－746,313,572－0</t>
+          <t>2,436,623,327＋517,384,278－763,190,839－0</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>2,143,621,745</t>
+          <t>2,190,816,766</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -2920,7 +3078,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>20.6810％</t>
+          <t>20.6798％</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -3534,7 +3692,7 @@
       <c r="H21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>計</t>
         </is>
@@ -3544,7 +3702,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="18" t="n">
         <v>27724</v>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -3552,10 +3710,10 @@
           <t>100.0％</t>
         </is>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="18" t="n">
         <v>9158</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="18" t="n">
         <v>9090</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -3763,10 +3921,10 @@
         <v>0.9913999999999999</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>27230</v>
+        <v>27539</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>26994.5</v>
+        <v>27300.9</v>
       </c>
       <c r="E32" s="11" t="n">
         <v>0</v>
@@ -3793,17 +3951,17 @@
         <v>1.0159</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>27230</v>
+        <v>27539</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>27662.7</v>
+        <v>27976.6</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>668.2</v>
+        <v>675.8</v>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>-161円</t>
+          <t>-163円</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr"/>
@@ -3823,17 +3981,17 @@
         <v>0.9692</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>27230</v>
+        <v>27539</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>26392.2</v>
+        <v>26691.7</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>-602.3</v>
+        <v>-609.2</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>+153円</t>
+          <t>+154円</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr"/>
@@ -3947,19 +4105,19 @@
           <t>標準給付費見込額（A）</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>9,815,032,090円</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>10,043,861,690円</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>9,519,211,524円</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>103.1％</t>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>105.5％</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3979,17 +4137,17 @@
           <t>地域支援事業費（B）</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>550,152,777円</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>593,658,000円</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>92.7％</t>
         </is>
@@ -4011,19 +4169,19 @@
           <t>合計（①）</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>10,365,184,867円</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>10,594,014,467円</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>10,112,869,524円</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>102.5％</t>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>104.8％</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -4043,19 +4201,19 @@
           <t>第1号被保険者負担分（C）</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>2,383,992,519円</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>2,436,623,327円</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>2,325,959,991円</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>102.5％</t>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>104.8％</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -4075,19 +4233,19 @@
           <t>調整交付金相当額（D）</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>505,942,798円</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>517,384,278円</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>492,515,476円</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>102.7％</t>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>105.0％</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -4107,19 +4265,19 @@
           <t>調整交付金見込額（E）</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>746,313,572円</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>763,190,839円</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>726,507,000円</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>102.7％</t>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>105.0％</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -4139,17 +4297,17 @@
           <t>基金取崩額（I）</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>0円</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>40,000,000円</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4171,19 +4329,19 @@
           <t>保険料収納必要額（J）</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>2,143,621,745円</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>2,190,816,766円</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>2,051,968,467円</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>104.5％</t>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>106.8％</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -4203,19 +4361,19 @@
           <t>補正後被保険者数（③）</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>26,995人</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>27,301人</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>26,871人</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>100.5％</t>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>101.6％</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -4235,17 +4393,17 @@
           <t>予定保険料収納率</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>99.0％</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>99.0％</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4257,7 +4415,7 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -4267,19 +4425,19 @@
           <t>算定上の月額基準額</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>6,684円</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>6,755円</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>6,428円</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>104.0％</t>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>105.1％</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -4373,17 +4531,17 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>9,267百万円（自然体推計）</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>+191円</t>
+          <t>9,483百万円（自然体推計・人口の基礎の置換え後）</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>+339円</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>累計 6619円</t>
+          <t>累計 6767円</t>
         </is>
       </c>
     </row>
@@ -4406,14 +4564,14 @@
           <t>550.2百万円（うち総合事業303.8百万円）</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>-29円</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>累計 6590円</t>
+          <t>累計 6738円</t>
         </is>
       </c>
     </row>
@@ -4436,14 +4594,14 @@
           <t>0円</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>+125円</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>累計 6715円</t>
+          <t>累計 6863円</t>
         </is>
       </c>
     </row>
@@ -4466,14 +4624,14 @@
           <t>0.9914（令和6年度実績）</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>-150円</t>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>-153円</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>累計 6565円</t>
+          <t>累計 6710円</t>
         </is>
       </c>
     </row>
@@ -4493,22 +4651,22 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>27,230人（推計上）</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>+119円</t>
+          <t>27,539人（推計上）</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>+45円</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>累計 6684円</t>
+          <t>累計 6755円</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="17" t="inlineStr"/>
+      <c r="A26" s="19" t="inlineStr"/>
       <c r="B26" s="14" t="inlineStr">
         <is>
           <t>基本ケース</t>
@@ -4524,14 +4682,14 @@
           <t>―</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>6684円</t>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>6755円</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>第9期の条例基準額6,400円に対し+284円</t>
+          <t>第9期の条例基準額6,400円に対し+355円</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4742,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>基本ケース6684円に対し、前提を1つずつ動かした場合の変化です。同時に複数を動かした場合は加法的にはなりません。</t>
+          <t>基本ケース6755円に対し、前提を1つずつ動かした場合の変化です。同時に複数を動かした場合は加法的にはなりません。</t>
         </is>
       </c>
     </row>
@@ -4651,12 +4809,12 @@
           <t>24％</t>
         </is>
       </c>
-      <c r="E6" s="18" t="n">
-        <v>7008</v>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>+323円</t>
+      <c r="E6" s="20" t="n">
+        <v>7081</v>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>+327円</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -4684,12 +4842,12 @@
           <t>22％</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
-        <v>6361</v>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>-323円</t>
+      <c r="E7" s="20" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>-327円</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -4717,12 +4875,12 @@
           <t>99.87％（令和6年度の現年度分実績）</t>
         </is>
       </c>
-      <c r="E8" s="18" t="n">
-        <v>6625</v>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>-59円</t>
+      <c r="E8" s="20" t="n">
+        <v>6695</v>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>-60円</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -4750,12 +4908,12 @@
           <t>6.490％（第8期の交付実績の水準）</t>
         </is>
       </c>
-      <c r="E9" s="18" t="n">
-        <v>6964</v>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>+279円</t>
+      <c r="E9" s="20" t="n">
+        <v>7037</v>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>+282円</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -4783,10 +4941,10 @@
           <t>1.0689（第9期計画）</t>
         </is>
       </c>
-      <c r="E10" s="18" t="n">
-        <v>6743</v>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="E10" s="20" t="n">
+        <v>6814</v>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>+59円</t>
         </is>
@@ -4808,7 +4966,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>自然体推計 9,267百万円</t>
+          <t>自然体推計（置換え後）9,483百万円</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -4816,12 +4974,12 @@
           <t>第9期の実績年率×3年 8,599百万円</t>
         </is>
       </c>
-      <c r="E11" s="18" t="n">
-        <v>6229</v>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>-455円</t>
+      <c r="E11" s="20" t="n">
+        <v>6159</v>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>-596円</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -4849,12 +5007,12 @@
           <t>1.0159（令和7年度実績）</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
-        <v>6523</v>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>-161円</t>
+      <c r="E12" s="20" t="n">
+        <v>6592</v>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>-163円</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -4882,10 +5040,10 @@
           <t>593,658,000円（第9期計画）</t>
         </is>
       </c>
-      <c r="E13" s="18" t="n">
-        <v>6716</v>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="E13" s="20" t="n">
+        <v>6786</v>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>+31円</t>
         </is>
@@ -4937,7 +5095,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="22" t="n">
+      <c r="A17" s="24" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -4951,10 +5109,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="18" t="n">
-        <v>6684</v>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="E17" s="20" t="n">
+        <v>6755</v>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>+0円</t>
         </is>
@@ -4980,12 +5138,12 @@
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="18" t="n">
-        <v>6902</v>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>+218円</t>
+      <c r="E18" s="20" t="n">
+        <v>6975</v>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>+220円</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -5009,12 +5167,12 @@
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="18" t="n">
-        <v>6229</v>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>-455円</t>
+      <c r="E19" s="20" t="n">
+        <v>6159</v>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>-596円</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -5038,12 +5196,12 @@
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="18" t="n">
-        <v>7287</v>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>+602円</t>
+      <c r="E20" s="20" t="n">
+        <v>7364</v>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>+609円</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -5067,12 +5225,12 @@
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="18" t="n">
-        <v>6602</v>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>-83円</t>
+      <c r="E21" s="20" t="n">
+        <v>6673</v>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>-82円</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -5085,7 +5243,7 @@
       <c r="A23" s="10" t="inlineStr">
         <is>
           <t>注1）感度は1つのレバーのみを動かしたものです。複数のレバーは相互に影響するため、組合せの結果は個々の差の合計とは一致しません。
-注2）最も大きいレバーは給付費の水準です。見える化システムの自然体推計と第9期の実績年率との間で月額に455円の幅があります。
+注2）最も大きいレバーは給付費の水準です。見える化システムの自然体推計と第9期の実績年率との間で月額に596円の幅があります。
 注3）予定収納率を実績に合わせる場合、滞納が生じたときの財源不足を基金で補う設計が前提となります。第9期は99.0％と保守的に置いていました。</t>
         </is>
       </c>
@@ -5173,7 +5331,7 @@
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="23" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -5201,7 +5359,7 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="23" t="n">
+      <c r="A7" s="25" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -5229,7 +5387,7 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="23" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -5257,7 +5415,7 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="23" t="n">
+      <c r="A9" s="25" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -5285,7 +5443,7 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -5294,7 +5452,7 @@
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>214362175</v>
+        <v>219081677</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
@@ -5308,7 +5466,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>基本ケースの保険料収納必要額2,143,621,745円による</t>
+          <t>基本ケースの保険料収納必要額2,190,816,766円による</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5510,7 @@
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="24" t="n">
+      <c r="A14" s="26" t="n">
         <v>1</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -5364,9 +5522,9 @@
         <v>0</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>6684</v>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
+        <v>6755</v>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>+0円</t>
         </is>
@@ -5378,7 +5536,7 @@
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="25" t="n">
         <v>2</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -5390,11 +5548,11 @@
         <v>26492172</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>6602</v>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>-83円</t>
+        <v>6673</v>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>-82円</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -5404,7 +5562,7 @@
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="25" t="n">
         <v>3</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -5413,24 +5571,24 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>17326843</v>
+        <v>12607341</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>6630</v>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>-54円</t>
+        <v>6716</v>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>-39円</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>残高は第10期の上限（暫定214,362,175円）まで下がる。上限の判定を計画期間ごとに行う場合の考え方</t>
+          <t>残高は第10期の上限（暫定219,081,677円）まで下がる。上限の判定を計画期間ごとに行う場合の考え方</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="25" t="n">
         <v>4</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -5442,11 +5600,11 @@
         <v>40000000</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>6560</v>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>-125円</t>
+        <v>6631</v>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>-123円</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -5456,7 +5614,7 @@
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="25" t="n">
         <v>5</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -5468,11 +5626,11 @@
         <v>231689018</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>5962</v>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>-722円</t>
+        <v>6040</v>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>-714円</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -5629,7 +5787,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>基本ケースの算定上の月額基準額6684円を百円未満四捨五入した6700円を基準額とした場合の、16段階の保険料です。第10期の段階数・乗率は政令改正により変わる可能性があります。</t>
+          <t>基本ケースの算定上の月額基準額6755円を百円未満四捨五入した6800円を基準額とした場合の、16段階の保険料です。第10期の段階数・乗率は政令改正により変わる可能性があります。</t>
         </is>
       </c>
     </row>
@@ -5701,16 +5859,16 @@
         <v>0.285</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>1909</v>
+        <v>1938</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>22900</v>
+        <v>23300</v>
       </c>
       <c r="F6" s="15" t="n">
         <v>21900</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1385</v>
@@ -5729,16 +5887,16 @@
         <v>0.439</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>2941</v>
+        <v>2985</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>35300</v>
+        <v>35800</v>
       </c>
       <c r="F7" s="15" t="n">
         <v>33700</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>1141</v>
@@ -5757,16 +5915,16 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>4590</v>
+        <v>4658</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>55100</v>
+        <v>55900</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>52600</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>887</v>
@@ -5787,23 +5945,23 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>5762</v>
+        <v>5848</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>69100</v>
+        <v>70200</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>66000</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>3100</v>
+        <v>4200</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>704</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>第5段階（基準）</t>
         </is>
@@ -5817,16 +5975,16 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>80400</v>
+        <v>81600</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>76800</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>3600</v>
+        <v>4800</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>1202</v>
@@ -5847,16 +6005,16 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>8442</v>
+        <v>8568</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>101300</v>
+        <v>102800</v>
       </c>
       <c r="F11" s="15" t="n">
         <v>96800</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>1363</v>
@@ -5877,16 +6035,16 @@
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>8777</v>
+        <v>8908</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>105300</v>
+        <v>106900</v>
       </c>
       <c r="F12" s="15" t="n">
         <v>100600</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>4700</v>
+        <v>6300</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>1261</v>
@@ -5907,16 +6065,16 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>10653</v>
+        <v>10812</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>127800</v>
+        <v>129700</v>
       </c>
       <c r="F13" s="15" t="n">
         <v>122100</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>5700</v>
+        <v>7600</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>550</v>
@@ -5937,16 +6095,16 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>10921</v>
+        <v>11084</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>131100</v>
+        <v>133000</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>125200</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>5900</v>
+        <v>7800</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>238</v>
@@ -5967,16 +6125,16 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>12730</v>
+        <v>12920</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>152800</v>
+        <v>155000</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>145900</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>6900</v>
+        <v>9100</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>105</v>
@@ -5997,16 +6155,16 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>14506</v>
+        <v>14722</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>174100</v>
+        <v>176700</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>166300</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>7800</v>
+        <v>10400</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>58</v>
@@ -6027,16 +6185,16 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>15846</v>
+        <v>16082</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>190100</v>
+        <v>193000</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>181600</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>8500</v>
+        <v>11400</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>37</v>
@@ -6057,16 +6215,16 @@
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>17186</v>
+        <v>17442</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>206200</v>
+        <v>209300</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>197000</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>9200</v>
+        <v>12300</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>27</v>
@@ -6087,16 +6245,16 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>17252</v>
+        <v>17510</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>207000</v>
+        <v>210100</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>197800</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>9200</v>
+        <v>12300</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>13</v>
@@ -6117,16 +6275,16 @@
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>17320</v>
+        <v>17578</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>207800</v>
+        <v>210900</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>198500</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>9300</v>
+        <v>12400</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>14</v>
@@ -6147,16 +6305,16 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>17386</v>
+        <v>17646</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>208600</v>
+        <v>211800</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>199300</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>9300</v>
+        <v>12500</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>105</v>
@@ -6227,10 +6385,10 @@
         </is>
       </c>
       <c r="E25" s="15" t="n">
-        <v>120867500</v>
+        <v>122701600</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>5428100</v>
+        <v>7262200</v>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr">
@@ -6259,10 +6417,10 @@
         </is>
       </c>
       <c r="E26" s="15" t="n">
-        <v>145287200</v>
+        <v>147504000</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>6509600</v>
+        <v>8726400</v>
       </c>
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr">
@@ -6291,10 +6449,10 @@
         </is>
       </c>
       <c r="E27" s="15" t="n">
-        <v>341145200</v>
+        <v>346252300</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>15195200</v>
+        <v>20302300</v>
       </c>
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
@@ -6319,10 +6477,10 @@
         </is>
       </c>
       <c r="E28" s="15" t="n">
-        <v>97447900</v>
+        <v>98892600</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>4370300</v>
+        <v>5815000</v>
       </c>
       <c r="G28" s="6" t="inlineStr"/>
       <c r="H28" s="6" t="inlineStr">
@@ -6334,7 +6492,7 @@
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>注1）第10期の月額基準額6700円は暫定の算定によるものです。条例で採用する基準額ではありません。
+          <t>注1）第10期の月額基準額6800円は暫定の算定によるものです。条例で採用する基準額ではありません。
 注2）第1〜3段階の公費軽減後の乗率は第9期の値です。第10期の軽減の内容は政令によります。
 注3）年額は百円未満を四捨五入しています。
 注4）令和7年度の被保険者数による試算であり、第10期の各年度の人数ではありません。</t>

--- a/output/第10期計画_将来推計_第3段階_給付費と保険料.xlsx
+++ b/output/第10期計画_将来推計_第3段階_給付費と保険料.xlsx
@@ -139,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,17 +188,23 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -207,9 +213,6 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -683,7 +686,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算額183,384,259円を3年分とする</t>
+          <t>令和6年度決算額177,161,259円を3年分とする</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1192,7 +1195,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>見える化システムは第10期3年平均の保険料基準額を6,238円と出力しています。本表の基本ケース6755円との差+517円について、受託者が確認できた範囲を示します。</t>
+          <t>見える化システムは第10期3年平均の保険料基準額を6,238円と出力しています。本表の基本ケース6740円との差+502円について、受託者が確認できた範囲を示します。</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1254,12 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>6755円</t>
+          <t>6740円</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>+517円</t>
+          <t>+502円</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1281,12 +1284,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>6159円</t>
+          <t>6144円</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>-79円</t>
+          <t>-94円</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1395,7 +1398,7 @@
     <row r="13" ht="140" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計6,238円は、内訳が出力されないため、項目ごとに突き合わせることができません。ただし、給付費を第9期の実績年率で置いた場合の本表の値は6159円で、6,238円との差は9円（0.1％）にとどまります。他の前提（収納率・基金取崩額・第1号負担割合）は同じであるため、見える化の保険料の推計は給付費を第9期の実績の水準で置いており、同じ見える化システムが出力する自然体給付費推計の伸びを織り込んでいない可能性があります。これは受託者の推定であり、確認したものではありません。
+          <t>見える化システムの自然体推計6,238円は、内訳が出力されないため、項目ごとに突き合わせることができません。ただし、給付費を第9期の実績年率で置いた場合の本表の値は6144円で、6,238円との差は9円（0.1％）にとどまります。他の前提（収納率・基金取崩額・第1号負担割合）は同じであるため、見える化の保険料の推計は給付費を第9期の実績の水準で置いており、同じ見える化システムが出力する自然体給付費推計の伸びを織り込んでいない可能性があります。これは受託者の推定であり、確認したものではありません。
 第10期の計画に用いる値は、見える化の出力をそのまま採るのではなく、本表のように内訳を組み立てたうえで決めることが必要です。内訳を示せなければ、住民及び委員に対して保険料の水準を説明することができないためです。
 計画素案 第6章第6節2に掲載している「見える化自然体推計（基準ケース）6,238円」は、本表の完成後に、本表の基本ケースへ置き換えることを提案します。</t>
         </is>
@@ -1527,7 +1530,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>1ポイントで約327円</t>
+          <t>1ポイントで約326円</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1617,7 +1620,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>-60円</t>
+          <t>-59円</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -1647,7 +1650,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>1％で約41円</t>
+          <t>1％で約40円</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1677,7 +1680,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>+31円（第9期計画の水準とした場合）</t>
+          <t>+44円（第9期計画の水準とした場合）</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1737,7 +1740,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>+282円（第8期の実績水準とした場合）</t>
+          <t>+283円（第8期の実績水準とした場合）</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1749,8 +1752,8 @@
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>注1）本表の基本ケース6755円は暫定の値です。上記9件が確定するまでは、条例で採用する基準額の算定には用いられません。
-注2）第9期の条例基準額は6,400円でした。本表の基本ケースはこれを+355円上回ります。
+          <t>注1）本表の基本ケース6740円は暫定の値です。上記9件が確定するまでは、条例で採用する基準額の算定には用いられません。
+注2）第9期の条例基準額は6,400円でした。本表の基本ケースはこれを+340円上回ります。
 注3）第10期の保険料は、水準そのものよりも「どの前提でその水準になるか」を示すことが重要です。本表は、前提を1つずつ確認できる形にすることを目的としています。</t>
         </is>
       </c>
@@ -1771,7 +1774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2210,92 +2213,466 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>【3　標準給付費見込額（A）】</t>
+          <t>【2の2　割増率の項目別の検算（国の様式との対照）】</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>令和6年度（円）</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>総給付費に対する率</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>出所</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>特定入所者介護サービス費　施設サービス居住費</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>14256897</v>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>0.5061％</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツール 実績値シート（3町計）</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>標準給付費見込額に含める項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>特定入所者介護サービス費　施設サービス食費</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>42152958</v>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>1.4963％</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツール 実績値シート（3町計）</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>標準給付費見込額に含める項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>特定入所者介護サービス費　短期入所の居住費・滞在費</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>938219</v>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>0.0333％</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツール 実績値シート（3町計）</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>標準給付費見込額に含める項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>特定入所者介護サービス費　短期入所の食費</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>18812372</v>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>0.6678％</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツール 実績値シート（3町計）</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>標準給付費見込額に含める項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>高額介護サービス費等給付額</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n">
+        <v>78686643</v>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>2.7931％</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツール 実績値シート（3町計）</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>標準給付費見込額に含める項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>高額医療合算介護サービス費等給付額</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>9305829</v>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>0.3303％</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツール 実績値シート（3町計）</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>標準給付費見込額に含める項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>算定対象審査支払手数料</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>2306369</v>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>0.0819％</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツール 実績値シート（3町計）</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>標準給付費見込額に含める項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>市町村特別給付費等</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>0.0000％</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツール 実績値シート（3町計）</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>標準給付費見込額に含める項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="14" t="inlineStr"/>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>加算計</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>166459287</v>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>5.9087％</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="14" t="inlineStr"/>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>総給付費＋加算計</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>2983653742</v>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>1.05909</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>項目の積上げによる標準給付費見込額</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="14" t="inlineStr"/>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>保険給付費（款2・令和6年度決算）</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="n">
+        <v>2983668988</v>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>1.05909</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>現行の割増率の算定に用いている値</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>-15246</v>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>0.000511％</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>決算の介護サービス等諸費2,817,209,701円と年報の給付費合計2,817,194,455円との差に一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>国の様式（介護保険事業計画作成支援ツール）では、標準給付費見込額は総給付費に特定入所者介護サービス費・高額介護サービス費・高額医療合算介護サービス費・審査支払手数料・市町村特別給付費を加えて求めます。本表の割増率1.05909は令和6年度の決算から求めたものですが、計画作成支援ツールの実績値シートによる項目の積上げでも1.05909となり、両者は一致します（差-15,246円・0.0005％）。割増率は単一の係数ではなく、上記5項目の合計として説明できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>【3　標準給付費見込額（A）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>第10期計</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>第9期計画との比</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>標準給付費見込額</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B43" s="20" t="n">
         <v>3286614092</v>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C43" s="20" t="n">
         <v>3348497337</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D43" s="20" t="n">
         <v>3408750262</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E43" s="20" t="n">
         <v>10043861690</v>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>105.5％</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>（参考）第9期計画</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
+      <c r="B44" s="15" t="n">
         <v>3127780210</v>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C44" s="15" t="n">
         <v>3184593217</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D44" s="15" t="n">
         <v>3206838097</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="E44" s="15" t="n">
         <v>9519211524</v>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>100.0％</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="68" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="46" ht="68" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>注1）単位は円。第10期の標準給付費見込額は第9期計画の105.5％です。
 注2）割増率は、高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるためのものです。令和6年度の決算では、給付費2,817,194,455円に対し保険給付費（款2）が2,983,668,988円で、差は166,474,533円です。
@@ -2304,15 +2681,17 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2406,7 +2785,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>55.2％</t>
+          <t>57.2％</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -2432,7 +2811,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>41.4％</t>
+          <t>42.8％</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -2484,7 +2863,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2.3％</t>
+          <t>2.4％</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -2499,13 +2878,13 @@
           <t>計</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="20" t="n">
         <v>186011000</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="20" t="n">
         <v>183384259</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="20" t="n">
         <v>2626741</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -2564,21 +2943,21 @@
           <t>地域支援事業費</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
-        <v>183384259</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>183384259</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>183384259</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>550152777</v>
+      <c r="B14" s="20" t="n">
+        <v>177161259</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <v>177161259</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>177161259</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>531483777</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>92.7％</t>
+          <t>89.5％</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2988,7 @@
     <row r="17" ht="76" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>注1）第9期計画の地域支援事業費は各年度197,886,000円でしたが、令和6年度の決算額は183,384,259円で、計画の92.7％にとどまりました。
+          <t>注1）第9期計画の地域支援事業費は各年度197,886,000円でしたが、令和6年度の決算額は177,161,259円で、計画の89.5％にとどまりました。
 注2）見える化システムの保険料基準額でも、第9期の地域支援事業費は計画428円（月額換算）に対し実績433円です（計画素案 第6章第6節）。決算と見える化とで方向が異なるのは、見える化の月額換算が補正後被保険者数を分母としているためです。
 注3）第10期の地域支援事業費は、包括的支援事業6事業及び任意事業の事業別実績を受領したうえで、事業設計に基づいて置き直します。本表の値は暫定です。</t>
         </is>
@@ -2633,7 +3012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2721,7 +3100,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>自然体給付費×割増率1.0591</t>
+          <t>自然体給付費×割増率1.0591（01シートで項目別に検算）</t>
         </is>
       </c>
     </row>
@@ -2737,24 +3116,24 @@
         </is>
       </c>
       <c r="C7" s="15" t="n">
-        <v>550152777</v>
+        <v>531483777</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>593658000</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>92.7％</t>
+          <t>89.5％</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算額×3年</t>
+          <t>令和6年度決算額×3年。保険者機能強化推進事業費及び保険者努力支援事業費は交付金を財源とするため除く</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>①</t>
         </is>
@@ -2764,15 +3143,15 @@
           <t>合計（A＋B）</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n">
-        <v>10594014467</v>
-      </c>
-      <c r="D8" s="18" t="n">
+      <c r="C8" s="20" t="n">
+        <v>10575345467</v>
+      </c>
+      <c r="D8" s="20" t="n">
         <v>10112869524</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>104.8％</t>
+          <t>104.6％</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -2782,7 +3161,7 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>②</t>
         </is>
@@ -2792,15 +3171,15 @@
           <t>調整交付金の算定基礎（A＋総合事業費）</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n">
-        <v>10347685553</v>
-      </c>
-      <c r="D9" s="18" t="n">
+      <c r="C9" s="20" t="n">
+        <v>10365249644</v>
+      </c>
+      <c r="D9" s="20" t="n">
         <v>9850309520</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>105.0％</t>
+          <t>105.2％</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -2821,14 +3200,14 @@
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>2436623327</v>
+        <v>2432329457</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>2325959991</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>104.8％</t>
+          <t>104.6％</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -2849,14 +3228,14 @@
         </is>
       </c>
       <c r="C11" s="15" t="n">
-        <v>517384278</v>
+        <v>518262482</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>492515476</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>105.0％</t>
+          <t>105.2％</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -2877,14 +3256,14 @@
         </is>
       </c>
       <c r="C12" s="15" t="n">
-        <v>763190839</v>
+        <v>764486274</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>726507000</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>105.0％</t>
+          <t>105.2％</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2896,200 +3275,284 @@
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>財政調整基金取崩額</t>
+          <t>財政安定化基金拠出金見込額</t>
         </is>
       </c>
       <c r="C13" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>拠出の予定がないため0円</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>財政安定化基金償還金</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>借入れの実績がないため0円</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>市町村相互財政安定化事業負担額</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>同事業に参加していないため0円</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>財政調整基金取崩額</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15" t="n">
         <v>40000000</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>0.0％</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>基本ケースは0円。07シート参照</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>保険料収納必要額（C＋D－E－I）</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>2190816766</v>
-      </c>
-      <c r="D14" s="18" t="n">
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>保険料収納必要額（C＋D－E＋F＋G±H－I）</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="n">
+        <v>2186105666</v>
+      </c>
+      <c r="D17" s="20" t="n">
         <v>2051968467</v>
       </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>106.8％</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>106.5％</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>【2　検算】</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>検算の内容</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>式</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>J＝C＋D－E－I</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>2,436,623,327＋517,384,278－763,190,839－0</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>2,190,816,766</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>一致</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>第9期の同じ式の再現</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>2,325,959,991＋492,515,476－726,507,000－40,000,000</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>2,051,968,467</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>一致</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>第9期の月額基準額の再現</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>J÷収納率÷③÷12</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>6427.9円（公表値6,428円）</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>一致</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>J＝C＋D－E＋F＋G±H－I（F・G・Hはいずれも0）</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>2,432,329,457＋518,262,482－764,486,274－0</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>2,186,105,666</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>第9期の同じ式の再現</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>2,325,959,991＋492,515,476－726,507,000－40,000,000</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>2,051,968,467</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>第9期の月額基準額の再現</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>J÷収納率÷③÷12</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>6427.9円（公表値6,428円）</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>①に対するJの割合</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>（負担割合23％＋②÷①×（5％－見込交付割合7.375％））</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>20.6798％</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>20.6717％</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
-    </row>
-    <row r="23" ht="68" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="68" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>注1）第1号被保険者負担割合は、第9期は23％でした。第10期の割合は政令により定まります。1ポイントの違いが月額に与える影響は06シートに示します。
 注2）調整交付金見込額（E）は、第9期計画の見込交付割合（令和6年度7.51％・令和7年度7.43％・令和8年度7.19％）と同水準の7.375％で置いています。見える化システムによる交付の実績は第7期が計画の90％、第8期が88％であり、いずれも計画を下回りました。実績の水準で置いた場合は06シートに示します。</t>
@@ -3099,10 +3562,10 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3692,7 +4155,7 @@
       <c r="H21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>計</t>
         </is>
@@ -3702,7 +4165,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C22" s="18" t="n">
+      <c r="C22" s="20" t="n">
         <v>27724</v>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -3710,10 +4173,10 @@
           <t>100.0％</t>
         </is>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="20" t="n">
         <v>9158</v>
       </c>
-      <c r="F22" s="18" t="n">
+      <c r="F22" s="20" t="n">
         <v>9090</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -4105,17 +4568,17 @@
           <t>標準給付費見込額（A）</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>10,043,861,690円</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>9,519,211,524円</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>105.5％</t>
         </is>
@@ -4137,19 +4600,19 @@
           <t>地域支援事業費（B）</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>550,152,777円</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>531,483,777円</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>593,658,000円</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>92.7％</t>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>89.5％</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -4169,19 +4632,19 @@
           <t>合計（①）</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>10,594,014,467円</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>10,575,345,467円</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>10,112,869,524円</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>104.8％</t>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>104.6％</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -4201,19 +4664,19 @@
           <t>第1号被保険者負担分（C）</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>2,436,623,327円</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>2,432,329,457円</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>2,325,959,991円</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>104.8％</t>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>104.6％</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -4233,19 +4696,19 @@
           <t>調整交付金相当額（D）</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>517,384,278円</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>518,262,482円</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>492,515,476円</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>105.0％</t>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>105.2％</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -4265,19 +4728,19 @@
           <t>調整交付金見込額（E）</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>763,190,839円</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>764,486,274円</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>726,507,000円</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>105.0％</t>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>105.2％</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -4297,17 +4760,17 @@
           <t>基金取崩額（I）</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>0円</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>40,000,000円</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4329,19 +4792,19 @@
           <t>保険料収納必要額（J）</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>2,190,816,766円</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>2,186,105,666円</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>2,051,968,467円</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>106.8％</t>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>106.5％</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -4361,17 +4824,17 @@
           <t>補正後被保険者数（③）</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>27,301人</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>26,871人</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>101.6％</t>
         </is>
@@ -4393,17 +4856,17 @@
           <t>予定保険料収納率</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>99.0％</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>99.0％</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4415,7 +4878,7 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -4427,7 +4890,7 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>6,755円</t>
+          <t>6,740円</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -4437,7 +4900,7 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>105.1％</t>
+          <t>104.9％</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -4534,7 +4997,7 @@
           <t>9,483百万円（自然体推計・人口の基礎の置換え後）</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>+339円</t>
         </is>
@@ -4564,14 +5027,14 @@
           <t>550.2百万円（うち総合事業303.8百万円）</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>-29円</t>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>-44円</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>累計 6738円</t>
+          <t>累計 6723円</t>
         </is>
       </c>
     </row>
@@ -4594,14 +5057,14 @@
           <t>0円</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>+125円</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>累計 6863円</t>
+          <t>累計 6848円</t>
         </is>
       </c>
     </row>
@@ -4624,14 +5087,14 @@
           <t>0.9914（令和6年度実績）</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>-153円</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>累計 6710円</t>
+          <t>累計 6695円</t>
         </is>
       </c>
     </row>
@@ -4654,19 +5117,19 @@
           <t>27,539人（推計上）</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>+45円</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>累計 6755円</t>
+          <t>累計 6740円</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="19" t="inlineStr"/>
+      <c r="A26" s="23" t="inlineStr"/>
       <c r="B26" s="14" t="inlineStr">
         <is>
           <t>基本ケース</t>
@@ -4684,12 +5147,12 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>6755円</t>
+          <t>6740円</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>第9期の条例基準額6,400円に対し+355円</t>
+          <t>第9期の条例基準額6,400円に対し+340円</t>
         </is>
       </c>
     </row>
@@ -4742,7 +5205,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>基本ケース6755円に対し、前提を1つずつ動かした場合の変化です。同時に複数を動かした場合は加法的にはなりません。</t>
+          <t>基本ケース6740円に対し、前提を1つずつ動かした場合の変化です。同時に複数を動かした場合は加法的にはなりません。</t>
         </is>
       </c>
     </row>
@@ -4809,12 +5272,12 @@
           <t>24％</t>
         </is>
       </c>
-      <c r="E6" s="20" t="n">
-        <v>7081</v>
-      </c>
-      <c r="F6" s="22" t="inlineStr">
-        <is>
-          <t>+327円</t>
+      <c r="E6" s="19" t="n">
+        <v>7066</v>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>+326円</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -4842,12 +5305,12 @@
           <t>22％</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n">
-        <v>6428</v>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>-327円</t>
+      <c r="E7" s="19" t="n">
+        <v>6414</v>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>-326円</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -4875,12 +5338,12 @@
           <t>99.87％（令和6年度の現年度分実績）</t>
         </is>
       </c>
-      <c r="E8" s="20" t="n">
-        <v>6695</v>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>-60円</t>
+      <c r="E8" s="19" t="n">
+        <v>6681</v>
+      </c>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>-59円</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -4908,12 +5371,12 @@
           <t>6.490％（第8期の交付実績の水準）</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
-        <v>7037</v>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>+282円</t>
+      <c r="E9" s="19" t="n">
+        <v>7023</v>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>+283円</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -4941,10 +5404,10 @@
           <t>1.0689（第9期計画）</t>
         </is>
       </c>
-      <c r="E10" s="20" t="n">
-        <v>6814</v>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="E10" s="19" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>+59円</t>
         </is>
@@ -4974,10 +5437,10 @@
           <t>第9期の実績年率×3年 8,599百万円</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n">
-        <v>6159</v>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="E11" s="19" t="n">
+        <v>6144</v>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>-596円</t>
         </is>
@@ -5007,10 +5470,10 @@
           <t>1.0159（令和7年度実績）</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
-        <v>6592</v>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="E12" s="19" t="n">
+        <v>6577</v>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>-163円</t>
         </is>
@@ -5032,7 +5495,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>550,152,777円（令和6年度決算×3）</t>
+          <t>531,483,777円（令和6年度決算×3）</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -5040,12 +5503,12 @@
           <t>593,658,000円（第9期計画）</t>
         </is>
       </c>
-      <c r="E13" s="20" t="n">
-        <v>6786</v>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>+31円</t>
+      <c r="E13" s="19" t="n">
+        <v>6784</v>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>+44円</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -5095,7 +5558,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="26" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -5109,10 +5572,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="20" t="n">
-        <v>6755</v>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="E17" s="19" t="n">
+        <v>6740</v>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>+0円</t>
         </is>
@@ -5138,12 +5601,12 @@
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="20" t="n">
-        <v>6975</v>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>+220円</t>
+      <c r="E18" s="19" t="n">
+        <v>6961</v>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>+221円</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -5167,10 +5630,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="20" t="n">
-        <v>6159</v>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="E19" s="19" t="n">
+        <v>6144</v>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>-596円</t>
         </is>
@@ -5196,10 +5659,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="20" t="n">
-        <v>7364</v>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="E20" s="19" t="n">
+        <v>7349</v>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>+609円</t>
         </is>
@@ -5225,10 +5688,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="20" t="n">
-        <v>6673</v>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="E21" s="19" t="n">
+        <v>6659</v>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>-82円</t>
         </is>
@@ -5331,7 +5794,7 @@
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="25" t="n">
+      <c r="A6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -5359,7 +5822,7 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="25" t="n">
+      <c r="A7" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -5387,7 +5850,7 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -5415,7 +5878,7 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -5443,7 +5906,7 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -5452,7 +5915,7 @@
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>219081677</v>
+        <v>218610567</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
@@ -5466,7 +5929,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>基本ケースの保険料収納必要額2,190,816,766円による</t>
+          <t>基本ケースの保険料収納必要額2,186,105,666円による</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5973,7 @@
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="27" t="n">
         <v>1</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -5522,9 +5985,9 @@
         <v>0</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>6755</v>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
+        <v>6740</v>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>+0円</t>
         </is>
@@ -5536,7 +5999,7 @@
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -5548,9 +6011,9 @@
         <v>26492172</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>6673</v>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
+        <v>6659</v>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>-82円</t>
         </is>
@@ -5562,7 +6025,7 @@
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -5571,24 +6034,24 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>12607341</v>
+        <v>13078451</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>6716</v>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>-39円</t>
+        <v>6700</v>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>-40円</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>残高は第10期の上限（暫定219,081,677円）まで下がる。上限の判定を計画期間ごとに行う場合の考え方</t>
+          <t>残高は第10期の上限（暫定218,610,567円）まで下がる。上限の判定を計画期間ごとに行う場合の考え方</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -5600,9 +6063,9 @@
         <v>40000000</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>6631</v>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
+        <v>6617</v>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>-123円</t>
         </is>
@@ -5614,7 +6077,7 @@
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -5626,9 +6089,9 @@
         <v>231689018</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>6040</v>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
+        <v>6026</v>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>-714円</t>
         </is>
@@ -5787,7 +6250,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>基本ケースの算定上の月額基準額6755円を百円未満四捨五入した6800円を基準額とした場合の、16段階の保険料です。第10期の段階数・乗率は政令改正により変わる可能性があります。</t>
+          <t>基本ケースの算定上の月額基準額6740円を百円未満四捨五入した6700円を基準額とした場合の、16段階の保険料です。第10期の段階数・乗率は政令改正により変わる可能性があります。</t>
         </is>
       </c>
     </row>
@@ -5859,16 +6322,16 @@
         <v>0.285</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>1938</v>
+        <v>1909</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>23300</v>
+        <v>22900</v>
       </c>
       <c r="F6" s="15" t="n">
         <v>21900</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1385</v>
@@ -5887,16 +6350,16 @@
         <v>0.439</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>2985</v>
+        <v>2941</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>35800</v>
+        <v>35300</v>
       </c>
       <c r="F7" s="15" t="n">
         <v>33700</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>1141</v>
@@ -5915,16 +6378,16 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>4658</v>
+        <v>4590</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>55900</v>
+        <v>55100</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>52600</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>3300</v>
+        <v>2500</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>887</v>
@@ -5945,23 +6408,23 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>5848</v>
+        <v>5762</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>70200</v>
+        <v>69100</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>66000</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>4200</v>
+        <v>3100</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>704</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>第5段階（基準）</t>
         </is>
@@ -5975,16 +6438,16 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>81600</v>
+        <v>80400</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>76800</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>4800</v>
+        <v>3600</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>1202</v>
@@ -6005,16 +6468,16 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>8568</v>
+        <v>8442</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>102800</v>
+        <v>101300</v>
       </c>
       <c r="F11" s="15" t="n">
         <v>96800</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>1363</v>
@@ -6035,16 +6498,16 @@
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>8908</v>
+        <v>8777</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>106900</v>
+        <v>105300</v>
       </c>
       <c r="F12" s="15" t="n">
         <v>100600</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>6300</v>
+        <v>4700</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>1261</v>
@@ -6065,16 +6528,16 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>10812</v>
+        <v>10653</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>129700</v>
+        <v>127800</v>
       </c>
       <c r="F13" s="15" t="n">
         <v>122100</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>7600</v>
+        <v>5700</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>550</v>
@@ -6095,16 +6558,16 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>11084</v>
+        <v>10921</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>133000</v>
+        <v>131100</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>125200</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>7800</v>
+        <v>5900</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>238</v>
@@ -6125,16 +6588,16 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>12920</v>
+        <v>12730</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>155000</v>
+        <v>152800</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>145900</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>9100</v>
+        <v>6900</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>105</v>
@@ -6155,16 +6618,16 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>14722</v>
+        <v>14506</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>176700</v>
+        <v>174100</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>166300</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>10400</v>
+        <v>7800</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>58</v>
@@ -6185,16 +6648,16 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>16082</v>
+        <v>15846</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>193000</v>
+        <v>190100</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>181600</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>11400</v>
+        <v>8500</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>37</v>
@@ -6215,16 +6678,16 @@
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>17442</v>
+        <v>17186</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>209300</v>
+        <v>206200</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>197000</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>12300</v>
+        <v>9200</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>27</v>
@@ -6245,16 +6708,16 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>17510</v>
+        <v>17252</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>210100</v>
+        <v>207000</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>197800</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>12300</v>
+        <v>9200</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>13</v>
@@ -6275,16 +6738,16 @@
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>17578</v>
+        <v>17320</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>210900</v>
+        <v>207800</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>198500</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>12400</v>
+        <v>9300</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>14</v>
@@ -6305,16 +6768,16 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>17646</v>
+        <v>17386</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>211800</v>
+        <v>208600</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>199300</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>12500</v>
+        <v>9300</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>105</v>
@@ -6385,10 +6848,10 @@
         </is>
       </c>
       <c r="E25" s="15" t="n">
-        <v>122701600</v>
+        <v>120867500</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>7262200</v>
+        <v>5428100</v>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr">
@@ -6417,10 +6880,10 @@
         </is>
       </c>
       <c r="E26" s="15" t="n">
-        <v>147504000</v>
+        <v>145287200</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>8726400</v>
+        <v>6509600</v>
       </c>
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr">
@@ -6449,10 +6912,10 @@
         </is>
       </c>
       <c r="E27" s="15" t="n">
-        <v>346252300</v>
+        <v>341145200</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>20302300</v>
+        <v>15195200</v>
       </c>
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
@@ -6477,10 +6940,10 @@
         </is>
       </c>
       <c r="E28" s="15" t="n">
-        <v>98892600</v>
+        <v>97447900</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>5815000</v>
+        <v>4370300</v>
       </c>
       <c r="G28" s="6" t="inlineStr"/>
       <c r="H28" s="6" t="inlineStr">
@@ -6492,7 +6955,7 @@
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>注1）第10期の月額基準額6800円は暫定の算定によるものです。条例で採用する基準額ではありません。
+          <t>注1）第10期の月額基準額6700円は暫定の算定によるものです。条例で採用する基準額ではありません。
 注2）第1〜3段階の公費軽減後の乗率は第9期の値です。第10期の軽減の内容は政令によります。
 注3）年額は百円未満を四捨五入しています。
 注4）令和7年度の被保険者数による試算であり、第10期の各年度の人数ではありません。</t>
